--- a/excel-files/MAKATI/MAKATI HIGH SCHOOL.xlsx
+++ b/excel-files/MAKATI/MAKATI HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://depedph-my.sharepoint.com/personal/jonathan_buquia_deped_gov_ph/Documents/SAMPLE CONSOLIDATED FOLDER/MAKATI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE44C58D-37B6-457C-9A2F-CA19FA5DBA22}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1321B998-E8C5-4714-81FF-D5682700225D}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="0" windowWidth="14100" windowHeight="15390" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="0" windowWidth="14100" windowHeight="15390" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -3448,7 +3448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:10" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:10" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4395,7 +4395,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:10" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D51" s="10">
         <v>857</v>
@@ -4420,30 +4420,32 @@
       </c>
       <c r="H51" s="4">
         <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="10">
+        <v>835</v>
+      </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="12"/>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>835</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:10" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4451,12 +4453,14 @@
         <v>12</v>
       </c>
       <c r="C53" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D53" s="10">
         <v>857</v>
       </c>
-      <c r="E53" s="10"/>
+      <c r="E53" s="10">
+        <v>2024</v>
+      </c>
       <c r="F53" s="12" t="s">
         <v>20</v>
       </c>
@@ -4466,30 +4470,39 @@
       </c>
       <c r="H53" s="4">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="C54" s="10">
+        <v>835</v>
+      </c>
+      <c r="D54" s="10">
+        <v>857</v>
+      </c>
       <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
+      <c r="F54" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J54">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4497,12 +4510,14 @@
         <v>16</v>
       </c>
       <c r="C55" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D55" s="10">
         <v>857</v>
       </c>
-      <c r="E55" s="10"/>
+      <c r="E55" s="10">
+        <v>2025</v>
+      </c>
       <c r="F55" s="12" t="s">
         <v>20</v>
       </c>
@@ -4512,10 +4527,10 @@
       </c>
       <c r="H55" s="4">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4523,7 +4538,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D56" s="10">
         <v>857</v>
@@ -4538,10 +4553,10 @@
       </c>
       <c r="H56" s="4">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4549,12 +4564,14 @@
         <v>17</v>
       </c>
       <c r="C57" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D57" s="10">
         <v>857</v>
       </c>
-      <c r="E57" s="10"/>
+      <c r="E57" s="10">
+        <v>2025</v>
+      </c>
       <c r="F57" s="12" t="s">
         <v>20</v>
       </c>
@@ -4564,10 +4581,10 @@
       </c>
       <c r="H57" s="4">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4575,12 +4592,14 @@
         <v>22</v>
       </c>
       <c r="C58" s="10">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="D58" s="10">
         <v>857</v>
       </c>
-      <c r="E58" s="10"/>
+      <c r="E58" s="10">
+        <v>2025</v>
+      </c>
       <c r="F58" s="12" t="s">
         <v>20</v>
       </c>
@@ -4590,30 +4609,38 @@
       </c>
       <c r="H58" s="4">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="12"/>
+      <c r="C59" s="10">
+        <v>835</v>
+      </c>
+      <c r="D59" s="10">
+        <v>857</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H59" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4623,47 +4650,51 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:10" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="10">
+        <v>723</v>
+      </c>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
         <f t="shared" ref="G61:G69" si="12">IF((C61-D61)&lt;0,0,C61-D61)</f>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H61" s="4">
         <f t="shared" ref="H61:H69" si="13">IF((D61-C61)&lt;0,0,D61-C61)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:10" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="10">
+        <v>723</v>
+      </c>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H62" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:10" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4671,7 +4702,7 @@
         <v>12</v>
       </c>
       <c r="C63" s="10">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="D63" s="10">
         <v>594</v>
@@ -4684,14 +4715,14 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="H63" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:10" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4699,7 +4730,7 @@
         <v>21</v>
       </c>
       <c r="C64" s="10">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="D64" s="10">
         <v>594</v>
@@ -4712,7 +4743,7 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="13"/>
@@ -4726,13 +4757,15 @@
       <c r="B65" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="10">
+        <v>723</v>
+      </c>
       <c r="D65" s="10"/>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
       <c r="G65" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H65" s="4">
         <f t="shared" si="13"/>
@@ -4746,13 +4779,15 @@
       <c r="B66" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="10">
+        <v>723</v>
+      </c>
       <c r="D66" s="10"/>
       <c r="E66" s="10"/>
       <c r="F66" s="12"/>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
@@ -4766,13 +4801,15 @@
       <c r="B67" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="10">
+        <v>723</v>
+      </c>
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
       <c r="G67" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H67" s="4">
         <f t="shared" si="13"/>
@@ -4786,13 +4823,15 @@
       <c r="B68" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="10">
+        <v>723</v>
+      </c>
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
       <c r="G68" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H68" s="4">
         <f t="shared" si="13"/>
@@ -4806,13 +4845,15 @@
       <c r="B69" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="10">
+        <v>723</v>
+      </c>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="F69" s="12"/>
       <c r="G69" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H69" s="4">
         <f t="shared" si="13"/>
@@ -5216,17 +5257,25 @@
       <c r="B91" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="5"/>
+      <c r="C91" s="1">
+        <v>626</v>
+      </c>
+      <c r="D91" s="1">
+        <v>853</v>
+      </c>
+      <c r="E91" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G91" s="3">
         <f t="shared" ref="G91:G98" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
         <v>0</v>
       </c>
       <c r="H91" s="4">
         <f t="shared" ref="H91:H98" si="19">IF((D91-C91)&lt;0,0,D91-C91)</f>
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
@@ -5276,17 +5325,25 @@
       <c r="B94" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="5"/>
+      <c r="C94" s="1">
+        <v>582</v>
+      </c>
+      <c r="D94" s="1">
+        <v>853</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G94" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H94" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
@@ -5296,17 +5353,25 @@
       <c r="B95" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="5"/>
+      <c r="C95" s="1">
+        <v>582</v>
+      </c>
+      <c r="D95" s="1">
+        <v>853</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G95" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H95" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
@@ -5316,17 +5381,25 @@
       <c r="B96" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="5"/>
+      <c r="C96" s="1">
+        <v>626</v>
+      </c>
+      <c r="D96" s="1">
+        <v>853</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G96" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H96" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
@@ -5336,17 +5409,25 @@
       <c r="B97" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="5"/>
+      <c r="C97" s="1">
+        <v>582</v>
+      </c>
+      <c r="D97" s="1">
+        <v>853</v>
+      </c>
+      <c r="E97" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G97" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H97" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
@@ -5356,17 +5437,25 @@
       <c r="B98" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="5"/>
+      <c r="C98" s="1">
+        <v>626</v>
+      </c>
+      <c r="D98" s="1">
+        <v>853</v>
+      </c>
+      <c r="E98" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G98" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H98" s="4">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -5376,8 +5465,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E91:E98 E51:E59 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F91:F98 F51:F59 F71:F79 F81:F89 F2:F6 F8:F12 F61:F69" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -13624,8 +13713,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13643,7 +13732,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -21403,7 +21492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="39">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
@@ -21610,7 +21699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="39">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -22190,186 +22279,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22387,8 +22296,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 S103:S113 Y91:Y101 M91:M101 G91:G101 G103:G113 M115:M122 Y103:Y113 M103:M113 S91:S101" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 R103:R113 F103:F113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 X91:X101 X103:X113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 R91:R101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
